--- a/artfynd/A 4132-2026 artfynd.xlsx
+++ b/artfynd/A 4132-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70038075</v>
+        <v>56124544</v>
       </c>
       <c r="B2" t="n">
-        <v>98985</v>
+        <v>99141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219794</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rönngrund, 200 m N om vändplanen på skogsbilvägen, Upl</t>
+          <t>Halvön SO om Fårskär, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>643086</v>
+        <v>642846</v>
       </c>
       <c r="R2" t="n">
-        <v>6721380</v>
+        <v>6721267</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1999-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,27 +766,121 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Rikkärr</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Björn Dahlin</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114498815</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rönngrund, Gårdskärshalvön, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>643083</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6721135</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-08-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Andrahandsuppgift</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Press</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Andreas Press</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4132-2026 artfynd.xlsx
+++ b/artfynd/A 4132-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56124544</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,8 +891,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114498815</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>